--- a/docs/demo/Masari_Test_Results.xlsx
+++ b/docs/demo/Masari_Test_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"A*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"A*")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"A*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"A*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"A*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F4" s="3">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"B*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"B*")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"B*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"B*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"B*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F5" s="3">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"C*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"C*")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"C*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"C*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"C*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F6" s="3">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"D*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"D*")</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"D*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"D*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"D*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F7" s="3">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"E*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"E*")</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"E*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"E*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"E*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F8" s="3">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF(Results!$A$2:$A$66,"F*")</f>
+        <f>COUNTIF(Results!$A$2:$A$68,"F*")</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"F*",Results!$E$2:$E$66,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"PASS")</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"F*",Results!$E$2:$E$66,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"FAIL")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$66,"F*",Results!$E$2:$E$66,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"SKIP")</f>
         <v/>
       </c>
       <c r="F9" s="3">
@@ -765,7 +765,7 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Automated API suite</t>
@@ -773,7 +773,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>30 of 30 checks passed (roles, approvals, sign-up with documents, safety rules, and the existing story/feature smoke suites).</t>
+          <t>30 of 30 checks passed, re-run after the registration change (roles, approvals, sign-up with driver and shop-owner documents, safety rules, and the existing story/feature smoke suites).</t>
         </is>
       </c>
     </row>
@@ -809,87 +809,113 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>API 846, Admin 380, tooling 76 (2 skipped), app 632 - all passing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>PROBLEMS FOUND AND FIXED TODAY</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="75" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+          <t>API 854, Admin 380, tooling 76 (2 skipped), app 634 - all passing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Re-test after the registration change</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Only the sign-up rows (C01, C03, C13, C16, C17) and the Arabic sign-up screens were re-run on the emulator. The other emulator rows are from the 28 Oct run, before the change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>PROBLEMS FOUND AND FIXED</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>1. New accounts could never sign in</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Accounts created from an invitation have a phone number but no email, and sign-in only took an email. Now a verified phone number works (never for Admin accounts). Fixed in the API and the app's sign-in field.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>2. The trip map was blank (grey) until touched</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Probably the map problem you noticed. The map never requested its tiles for the route view. Fixed; verified with a request log.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>3. Small polish</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>3. Sign-up changed</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Create account now asks Normal user / Driver / Shop owner first. Shop owners upload their papers; every pending screen says review takes up to 24 hours. A passenger no longer signs up with an invitation code in the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>4. Small polish</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Arabic words on the English trip screen translated; zoom buttons no longer sit under the top buttons; the Admin site's missing browser icon added; the demo reset-key box now holds the real key.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>NOT TESTED BY ME</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="105" customHeight="1">
-      <c r="A24" s="7" t="inlineStr"/>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>A real phone (only the emulator); Arabic on every screen (checked the passenger home and sign-in); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage and the Download button in the browser; anything on a real server or real SMS.</t>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="165" customHeight="1">
+      <c r="A26" s="7" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>A real phone (only the emulator); Arabic on every screen (checked sign-in, the role chooser, the invitation and pending screens, and the three role homes; no stray English found apart from names and the demo consent text); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage, Download and the shop-owner Approve card in the browser; a normal user completing the email sign-up (needs a real email code); anything on a real server or real SMS.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B26:F26"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B22:F22"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -902,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1790,12 +1816,12 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Sign-in screen → "Create an invited account" → Passenger → enter the passenger invitation code and phone +970590002001 → Send verification code</t>
+          <t>Sign-in screen → "New to Masari? Create an account"</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>A code-entry screen appears with a resend countdown</t>
+          <t>A screen asks "How will you use Masari?" with three choices: Normal user, Driver, Shop owner. Normal user opens the email sign-up form; Driver and Shop owner open the invitation-code and phone screen with the role already chosen; Back returns to sign-in</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1805,7 +1831,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger invitation sign-up reaches the code screen.</t>
+          <t>Emulator, Arabic and English: Create account asks Normal user / Driver / Shop owner. Normal user opens the email form; Driver and Shop owner open the invitation screen with the role chosen; Back returns to sign-in.</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1880,12 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Enter the right code (from otp.txt), then name, a password of at least 15 characters, tick the three consents, Create account</t>
+          <t>Choose Shop owner (invitation code and +970590002003), enter the right code (from otp.txt), then name, a password of at least 15 characters, tick the three consents, Create account</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Account created; the passenger can sign in and is active straight away</t>
+          <t>Account created; the screen says the account is pending and an admin review usually takes up to 24 hours</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1869,7 +1895,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Emulator: account created, and the new passenger signs in with their phone number and password.</t>
+          <t>Emulator, Arabic and English: shop-owner account created; the screen says it is pending and review takes up to 24 hours.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1912,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Repeat C01–C03 for the driver (+970590002002)</t>
+          <t>Repeat for the driver (+970590002002)</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -2174,12 +2200,12 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Repeat C01–C03 for the merchant (+970590002003); Admin approves it (A09)</t>
+          <t>Admin approves the shop owner from C03 (A09), then sign in on the phone with their phone number and password</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Same pending → approved path; the merchant signs in</t>
+          <t>Same pending → approved path; the merchant home opens</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2189,7 +2215,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Emulator: merchant sign-up, pending, Admin approval, then phone sign-in to the merchant home.</t>
+          <t>Approval and phone sign-in to the merchant home were checked on the 28 Oct run (and the API suite repeats them); the sign-up entry is the new chooser, checked in C03.</t>
         </is>
       </c>
     </row>
@@ -2260,22 +2286,22 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up with invitation</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Passenger: open the seeded request and its match</t>
+          <t>Shop owner (pending, from C03): Add a document → choose licence.jpg (type "Commercial register")</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>The request and a match result are shown</t>
+          <t>The pending screen shows "Verification documents" asking for the commercial register, national ID and shop photo; the file appears in the list as "Commercial register · 1 KB"</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2285,29 +2311,29 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
+          <t>Emulator, Arabic and English: the shop owner sees the shop-papers card, uploads licence.jpg as Commercial register, and it is listed (1 KB). API: wrong kinds and fake files are refused, limit of six.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up with invitation</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Merchant: open the seeded order</t>
+          <t>In the Admin site, Users → the pending shop owner → Approve (or Reject)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Five parcels and their batch are shown</t>
+          <t>The shop owner's documents are listed with a Download button before you decide; the downloaded file opens and is the right file</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2317,14 +2343,14 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
+          <t>API: the Admin lists and downloads the shop owner's document as an attachment with identical bytes. The Approve card in the browser was not clicked.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2334,12 +2360,12 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
+          <t>Passenger: open the seeded request and its match</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>One combined passenger+parcel match exists, with a score breakdown</t>
+          <t>The request and a match result are shown</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2349,14 +2375,14 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
+          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2366,12 +2392,12 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Driver (the selected one): open the inbox</t>
+          <t>Merchant: open the seeded order</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>The match is there; the other driver's inbox is empty</t>
+          <t>Five parcels and their batch are shown</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2381,14 +2407,14 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
+          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2398,12 +2424,12 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Driver: accept the match</t>
+          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Exactly one trip is created</t>
+          <t>One combined passenger+parcel match exists, with a score breakdown</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2413,14 +2439,14 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Emulator: accepting creates exactly one trip.</t>
+          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2430,12 +2456,12 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
+          <t>Driver (the selected one): open the inbox</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Only the next valid action is offered each time</t>
+          <t>The match is there; the other driver's inbox is empty</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2445,14 +2471,14 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
+          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2462,12 +2488,12 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: open their trip</t>
+          <t>Driver: accept the match</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Both see the same trip and the same latest location; read-only</t>
+          <t>Exactly one trip is created</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2477,14 +2503,14 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
+          <t>Emulator: accepting creates exactly one trip.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -2494,12 +2520,12 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: bell and Notifications tab</t>
+          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
+          <t>Only the next valid action is offered each time</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2509,14 +2535,14 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
+          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2526,12 +2552,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Driver: complete the trip</t>
+          <t>Passenger and merchant: open their trip</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Trip shows completed on all three phones and in the Admin</t>
+          <t>Both see the same trip and the same latest location; read-only</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2541,14 +2567,14 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Emulator and API: trip Completed everywhere.</t>
+          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -2558,12 +2584,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Tracking wording</t>
+          <t>Passenger and merchant: bell and Notifications tab</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
+          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2573,29 +2599,29 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
+          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Main story (passenger, merchant, driver)</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Driver: Earnings/performance tab</t>
+          <t>Driver: complete the trip</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
+          <t>Trip shows completed on all three phones and in the Admin</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2605,29 +2631,29 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
+          <t>Emulator and API: trip Completed everywhere.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Main story (passenger, merchant, driver)</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Same tab, acceptance rate</t>
+          <t>Tracking wording</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
+          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -2637,14 +2663,14 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
+          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -2654,29 +2680,29 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
+          <t>Driver: Earnings/performance tab</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>The numbers in E02 move accordingly</t>
+          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
+          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -2686,12 +2712,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Merchant: Reports tab</t>
+          <t>Same tab, acceptance rate</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
+          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -2701,14 +2727,14 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
+          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -2718,29 +2744,29 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
+          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Confirmation; the sheet says it is not an emergency service</t>
+          <t>The numbers in E02 move accordingly</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
+          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -2750,12 +2776,12 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Send 11 reports without any being resolved</t>
+          <t>Merchant: Reports tab</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>The 11th is refused with a message about too many open reports</t>
+          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -2765,14 +2791,14 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>API: the 11th unresolved report is refused.</t>
+          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -2782,12 +2808,12 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Admin: Incidents</t>
+          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
+          <t>Confirmation; the sheet says it is not an emergency service</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -2797,14 +2823,14 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
+          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -2814,12 +2840,12 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Driver: go online/offline</t>
+          <t>Send 11 reports without any being resolved</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>The state changes once per tap and survives closing the app</t>
+          <t>The 11th is refused with a message about too many open reports</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -2829,29 +2855,29 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
+          <t>API: the 11th unresolved report is refused.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Smaller features</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
+          <t>Admin: Incidents</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -2861,29 +2887,29 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
+          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Smaller features</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>A pending merchant or driver signs in on the phone</t>
+          <t>Driver: go online/offline</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Refused with a clear message</t>
+          <t>The state changes once per tap and survives closing the app</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -2893,14 +2919,14 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>API and emulator: pending merchant and driver cannot sign in.</t>
+          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -2910,7 +2936,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
+          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -2925,14 +2951,14 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>API: rejected driver and disabled merchant cannot sign in.</t>
+          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -2942,12 +2968,12 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
+          <t>A pending merchant or driver signs in on the phone</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Not reachable</t>
+          <t>Refused with a clear message</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2957,14 +2983,14 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
+          <t>API and emulator: pending merchant and driver cannot sign in.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -2974,12 +3000,12 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>No: uploading is closed once a decision is made</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -2989,45 +3015,109 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>API: once approved or rejected, uploads are refused.</t>
+          <t>API: rejected driver and disabled merchant cannot sign in.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Not reachable</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>No: uploading is closed once a decision is made</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>API: once approved or rejected, uploads are refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Must NOT work (safety)</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Look through every screen for the words "push notification", "emergency", "live GPS", "payment", "earnings" used as if they work</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>None claim a feature that is not built</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Spot check of the screens: no claim of push, live GPS, payments or emergency response; earnings say not tracked.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F66"/>
-  <conditionalFormatting sqref="E2:E66">
+  <autoFilter ref="A1:F68"/>
+  <conditionalFormatting sqref="E2:E68">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>

--- a/docs/demo/Masari_Test_Results.xlsx
+++ b/docs/demo/Masari_Test_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"A*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"A*")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"A*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F4" s="3">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"B*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"B*")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"B*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F5" s="3">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"C*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"C*")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"C*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F6" s="3">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"D*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"D*")</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"D*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F7" s="3">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"E*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"E*")</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"E*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F8" s="3">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF(Results!$A$2:$A$68,"F*")</f>
+        <f>COUNTIF(Results!$A$2:$A$69,"F*")</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"PASS")</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"FAIL")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$68,"F*",Results!$E$2:$E$68,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"SKIP")</f>
         <v/>
       </c>
       <c r="F9" s="3">
@@ -821,7 +821,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Only the sign-up rows (C01, C03, C13, C16, C17) and the Arabic sign-up screens were re-run on the emulator. The other emulator rows are from the 28 Oct run, before the change.</t>
+          <t>Only the sign-up rows (C01, C03, C13, C16, C17, C18) and the Arabic sign-up screens were re-run on the emulator. The other emulator rows are from the 28 Oct run, before the change.</t>
         </is>
       </c>
     </row>
@@ -897,11 +897,11 @@
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
     </row>
-    <row r="26" ht="165" customHeight="1">
+    <row r="26" ht="150" customHeight="1">
       <c r="A26" s="7" t="inlineStr"/>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A real phone (only the emulator); Arabic on every screen (checked sign-in, the role chooser, the invitation and pending screens, and the three role homes; no stray English found apart from names and the demo consent text); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage, Download and the shop-owner Approve card in the browser; a normal user completing the email sign-up (needs a real email code); anything on a real server or real SMS.</t>
+          <t>A real phone (only the emulator); Arabic on every screen (checked sign-in, the role chooser, the invitation and pending screens, and the three role homes; no stray English found apart from names and the demo consent text); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage, Download and the shop-owner Approve card in the browser; a normal user's sign-up with a real email and a real SMS; anything on a real server or real SMS.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2350,22 +2350,22 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up with invitation</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Passenger: open the seeded request and its match</t>
+          <t>Create account → Normal user → name, an email ending in @example.com, a password of at least 12 characters → Sign up; paste the token from email-codes.txt, tick the three documents, Continue; then enter a phone such as +970590003020, Send code, type the code from otp.txt, Continue</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>The request and a match result are shown</t>
+          <t>The passenger home opens; no invitation code and no admin approval were needed</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2375,14 +2375,14 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
+          <t>Emulator, English: Normal user -&gt; email sign-up -&gt; token from email-codes.txt -&gt; three documents -&gt; phone check with the code from otp.txt -&gt; passenger home. Run after making the demo write email and phone codes to files.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Merchant: open the seeded order</t>
+          <t>Passenger: open the seeded request and its match</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>Five parcels and their batch are shown</t>
+          <t>The request and a match result are shown</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2407,14 +2407,14 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
+          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
+          <t>Merchant: open the seeded order</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>One combined passenger+parcel match exists, with a score breakdown</t>
+          <t>Five parcels and their batch are shown</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2439,14 +2439,14 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
+          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Driver (the selected one): open the inbox</t>
+          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>The match is there; the other driver's inbox is empty</t>
+          <t>One combined passenger+parcel match exists, with a score breakdown</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2471,14 +2471,14 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
+          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Driver: accept the match</t>
+          <t>Driver (the selected one): open the inbox</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Exactly one trip is created</t>
+          <t>The match is there; the other driver's inbox is empty</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Emulator: accepting creates exactly one trip.</t>
+          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
+          <t>Driver: accept the match</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Only the next valid action is offered each time</t>
+          <t>Exactly one trip is created</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2535,14 +2535,14 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
+          <t>Emulator: accepting creates exactly one trip.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: open their trip</t>
+          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Both see the same trip and the same latest location; read-only</t>
+          <t>Only the next valid action is offered each time</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2567,14 +2567,14 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
+          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: bell and Notifications tab</t>
+          <t>Passenger and merchant: open their trip</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
+          <t>Both see the same trip and the same latest location; read-only</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2599,14 +2599,14 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
+          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Driver: complete the trip</t>
+          <t>Passenger and merchant: bell and Notifications tab</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Trip shows completed on all three phones and in the Admin</t>
+          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Emulator and API: trip Completed everywhere.</t>
+          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Tracking wording</t>
+          <t>Driver: complete the trip</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
+          <t>Trip shows completed on all three phones and in the Admin</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -2663,29 +2663,29 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
+          <t>Emulator and API: trip Completed everywhere.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Main story (passenger, merchant, driver)</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Driver: Earnings/performance tab</t>
+          <t>Tracking wording</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
+          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
+          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Same tab, acceptance rate</t>
+          <t>Driver: Earnings/performance tab</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
+          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -2727,14 +2727,14 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
+          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -2744,29 +2744,29 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
+          <t>Same tab, acceptance rate</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>The numbers in E02 move accordingly</t>
+          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
+          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -2776,29 +2776,29 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Merchant: Reports tab</t>
+          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
+          <t>The numbers in E02 move accordingly</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
+          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
+          <t>Merchant: Reports tab</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Confirmation; the sheet says it is not an emergency service</t>
+          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
+          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Send 11 reports without any being resolved</t>
+          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>The 11th is refused with a message about too many open reports</t>
+          <t>Confirmation; the sheet says it is not an emergency service</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -2855,14 +2855,14 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>API: the 11th unresolved report is refused.</t>
+          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Admin: Incidents</t>
+          <t>Send 11 reports without any being resolved</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
+          <t>The 11th is refused with a message about too many open reports</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
+          <t>API: the 11th unresolved report is refused.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Driver: go online/offline</t>
+          <t>Admin: Incidents</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>The state changes once per tap and survives closing the app</t>
+          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -2919,29 +2919,29 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
+          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Smaller features</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
+          <t>Driver: go online/offline</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>The state changes once per tap and survives closing the app</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2951,14 +2951,14 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
+          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>A pending merchant or driver signs in on the phone</t>
+          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Refused with a clear message</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2983,14 +2983,14 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>API and emulator: pending merchant and driver cannot sign in.</t>
+          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
+          <t>A pending merchant or driver signs in on the phone</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Refused with a clear message</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3015,14 +3015,14 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>API: rejected driver and disabled merchant cannot sign in.</t>
+          <t>API and emulator: pending merchant and driver cannot sign in.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
+          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Not reachable</t>
+          <t>Refused</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
+          <t>API: rejected driver and disabled merchant cannot sign in.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>No: uploading is closed once a decision is made</t>
+          <t>Not reachable</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3079,45 +3079,77 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>API: once approved or rejected, uploads are refused.</t>
+          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>No: uploading is closed once a decision is made</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>API: once approved or rejected, uploads are refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>Must NOT work (safety)</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>Look through every screen for the words "push notification", "emergency", "live GPS", "payment", "earnings" used as if they work</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>None claim a feature that is not built</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>Spot check of the screens: no claim of push, live GPS, payments or emergency response; earnings say not tracked.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F68"/>
-  <conditionalFormatting sqref="E2:E68">
+  <autoFilter ref="A1:F69"/>
+  <conditionalFormatting sqref="E2:E69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>

--- a/docs/demo/Masari_Test_Results.xlsx
+++ b/docs/demo/Masari_Test_Results.xlsx
@@ -2360,7 +2360,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Create account → Normal user → name, an email ending in @example.com, a password of at least 12 characters → Sign up; paste the token from email-codes.txt, tick the three documents, Continue; then enter a phone such as +970590003020, Send code, type the code from otp.txt, Continue</t>
+          <t>Create account → Normal user → name, an email ending in @example.com, a password of at least 12 characters → Sign up; type the six-digit code from email-codes.txt, tick the three documents, Continue; then enter a phone such as +970590003020, Send code, type the code from otp.txt, Continue</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">

--- a/docs/demo/Masari_Test_Results.xlsx
+++ b/docs/demo/Masari_Test_Results.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$F$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Masari test results - 28 Oct 2026 (run by Claude, not by you)</t>
+          <t>Masari test results - 28 Oct 2026, extended 29 Oct 2026 (run by Claude, not by you)</t>
         </is>
       </c>
     </row>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"A*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"A*")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"A*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"A*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"A*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"A*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F4" s="3">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"B*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"B*")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"B*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"B*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"B*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"B*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F5" s="3">
@@ -621,23 +621,23 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"C*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"C*")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"C*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"C*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"C*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"C*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F6" s="3">
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"D*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"D*")</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"D*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"D*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"D*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"D*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F7" s="3">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"E*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"E*")</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"E*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"E*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"E*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"E*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F8" s="3">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF(Results!$A$2:$A$69,"F*")</f>
+        <f>COUNTIF(Results!$A$2:$A$130,"F*")</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"PASS")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"F*",Results!$E$2:$E$130,"PASS")</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"FAIL")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"F*",Results!$E$2:$E$130,"FAIL")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS(Results!$A$2:$A$69,"F*",Results!$E$2:$E$69,"SKIP")</f>
+        <f>COUNTIFS(Results!$A$2:$A$130,"F*",Results!$E$2:$E$130,"SKIP")</f>
         <v/>
       </c>
       <c r="F9" s="3">
@@ -765,7 +765,7 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="105" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Automated API suite</t>
@@ -773,7 +773,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>30 of 30 checks passed, re-run after the registration change (roles, approvals, sign-up with driver and shop-owner documents, safety rules, and the existing story/feature smoke suites).</t>
+          <t>71 of 71 checks passed on 29 Oct (the 30 older ones plus the new-feature checks: six-digit email codes, open sign-up and Send for review, route fares, passenger parcels, bulk orders, AI assistant, delivery handover code, ratings and trust score, approaching alert, document expiry and renewal, success metrics and the simulated comparison).</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Unit tests</t>
@@ -809,113 +809,139 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>API 854, Admin 380, tooling 76 (2 skipped), app 634 - all passing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>API 1155 and repository tooling 84 (2 skipped) all passing on 29 Oct; the Admin site and app tests were not re-run in this pass (those apps were not changed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>New-feature pass, 29 Oct</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Every new row (A20-A21, C31-C39, E14-E42, F08-F10) was checked through the live demo API only. The screens for these features were not driven on the emulator or in the browser, and rows left blank (C19-C29, E09-E13, F07) were not re-run in this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>Re-test after the registration change</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Only the sign-up rows (C01, C03, C13, C16, C17, C18) and the Arabic sign-up screens were re-run on the emulator. The other emulator rows are from the 28 Oct run, before the change.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>PROBLEMS FOUND AND FIXED</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="75" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>1. New accounts could never sign in</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Accounts created from an invitation have a phone number but no email, and sign-in only took an email. Now a verified phone number works (never for Admin accounts). Fixed in the API and the app's sign-in field.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>2. The trip map was blank (grey) until touched</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Probably the map problem you noticed. The map never requested its tiles for the route view. Fixed; verified with a request log.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="75" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>3. Sign-up changed</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>Create account now asks Normal user / Driver / Shop owner first. Shop owners upload their papers; every pending screen says review takes up to 24 hours. A passenger no longer signs up with an invitation code in the app.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>4. Small polish</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Arabic words on the English trip screen translated; zoom buttons no longer sit under the top buttons; the Admin site's missing browser icon added; the demo reset-key box now holds the real key.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>5. Demo reset failed after route fares were set (29 Oct)</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>The reset of the demo data did not clear the fare history, so it answered 500 once an Admin had set a route fare. Fixed in the API (with a test); the test environment now also turns on the route switches and marks the automated sign-up phone numbers as demo data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>NOT TESTED BY ME</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="7" t="inlineStr"/>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>A real phone (only the emulator); Arabic on every screen (checked sign-in, the role chooser, the invitation and pending screens, and the three role homes; no stray English found apart from names and the demo consent text); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage, Download and the shop-owner Approve card in the browser; a normal user's sign-up with a real email and a real SMS; anything on a real server or real SMS.</t>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="195" customHeight="1">
+      <c r="A28" s="7" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>A real phone (only the emulator); real SMS and real email delivery (codes are read from files); the new-feature screens on the emulator and in the browser (only their API was checked); Arabic on every screen (checked sign-in, the role chooser, the invitation and pending screens, and the three role homes; no stray English found apart from names and the demo consent text); the percentage display of the acceptance rate; simulated tracking steps on the phone; opening the CSV files in Excel; clicking Admin triage, Download and the shop-owner Approve card in the browser; a normal user's sign-up with a real email and a real SMS; anything on a real server or real SMS.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -928,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1582,22 +1608,22 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Phone: signing in</t>
+          <t>Admin site</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Open the app</t>
+          <t>Reports page → Success metrics (or GET /api/v1/admin/success-metrics, and /export for the CSV): open it as the Admin, then try it as a passenger and without signing in</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Sign-in screen, Arabic by default, right-to-left</t>
+          <t>Admin: figures for the last 30 days with the previous period for comparison, a CSV download; passenger: refused (403); not signed in: 401; a start date after the end date, or a range over a year, is refused</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1607,29 +1633,29 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Emulator: fresh install opens the sign-in screen in Arabic.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): admin only (403 passenger, 401 anonymous); shape has range, generated_at and metrics with no personal data; reversed and over-a-year ranges refused; the CSV export is a text/csv attachment. The Reports page was not opened in the browser.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Phone: signing in</t>
+          <t>Admin site</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Switch to English with the globe icon</t>
+          <t>Matching / Batching page → Simulated comparison tab (or GET /api/v1/compare/simulation?seed=7)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Everything flips to English, left-to-right; switch back works</t>
+          <t>Manual, nearest-driver and Masari results, labelled as simulated; the same seed always gives the same numbers, another seed differs; nothing is written; passengers cannot call it</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1639,14 +1665,14 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Emulator: switches to English and back.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): admin only; the same seed gives byte-identical results, another seed differs; all three methods present; a bad seed is refused. The Matching page tab was not opened in the browser.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1656,12 +1682,12 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Wrong email/password</t>
+          <t>Open the app</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>A clear "incorrect" message, not a crash or a network error</t>
+          <t>Sign-in screen, Arabic by default, right-to-left</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1671,14 +1697,14 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>Emulator: wrong password shows a clear message.</t>
+          <t>Emulator: fresh install opens the sign-in screen in Arabic.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1688,12 +1714,12 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Sign in as the demo passenger</t>
+          <t>Switch to English with the globe icon</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Passenger home opens</t>
+          <t>Everything flips to English, left-to-right; switch back works</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1703,14 +1729,14 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Emulator: demo passenger signs in and out.</t>
+          <t>Emulator: switches to English and back.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1720,12 +1746,12 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Sign out, sign in as the demo driver, then the demo merchant</t>
+          <t>Wrong email/password</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Each role sees its own home and tabs, and none of the other roles' screens</t>
+          <t>A clear "incorrect" message, not a crash or a network error</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1735,14 +1761,14 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>Emulator: demo driver and demo merchant each reach their own home and sign out.</t>
+          <t>Emulator: wrong password shows a clear message.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1752,12 +1778,12 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Close the app completely and reopen it</t>
+          <t>Sign in as the demo passenger</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>You are still signed in (or sent to sign-in, but never to a broken screen)</t>
+          <t>Passenger home opens</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1767,14 +1793,14 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Emulator: closing and reopening the app keeps you signed in.</t>
+          <t>Emulator: demo passenger signs in and out.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1784,12 +1810,12 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Turn the emulator's internet off (airplane mode) and open a list</t>
+          <t>Sign out, sign in as the demo driver, then the demo merchant</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>A friendly offline/error message with a retry; no crash</t>
+          <t>Each role sees its own home and tabs, and none of the other roles' screens</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1799,29 +1825,29 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Emulator: with no internet, signing in shows 'Network unavailable...'; it works again when the internet returns.</t>
+          <t>Emulator: demo driver and demo merchant each reach their own home and sign out.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: signing in</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Sign-in screen → "New to Masari? Create an account"</t>
+          <t>Close the app completely and reopen it</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>A screen asks "How will you use Masari?" with three choices: Normal user, Driver, Shop owner. Normal user opens the email sign-up form; Driver and Shop owner open the invitation-code and phone screen with the role already chosen; Back returns to sign-in</t>
+          <t>You are still signed in (or sent to sign-in, but never to a broken screen)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1831,29 +1857,29 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Emulator, Arabic and English: Create account asks Normal user / Driver / Shop owner. Normal user opens the email form; Driver and Shop owner open the invitation screen with the role chosen; Back returns to sign-in.</t>
+          <t>Emulator: closing and reopening the app keeps you signed in.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: signing in</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Enter a wrong code</t>
+          <t>Turn the emulator's internet off (airplane mode) and open a list</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>A clear error; you can try again</t>
+          <t>A friendly offline/error message with a retry; no crash</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1863,29 +1889,29 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>API: a wrong one-time code is refused.</t>
+          <t>Emulator: with no internet, signing in shows 'Network unavailable...'; it works again when the internet returns.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Choose Shop owner (invitation code and +970590002003), enter the right code (from otp.txt), then name, a password of at least 15 characters, tick the three consents, Create account</t>
+          <t>Sign-in screen → "New to Masari? Create an account"</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Account created; the screen says the account is pending and an admin review usually takes up to 24 hours</t>
+          <t>A screen asks "How will you use Masari?" with three choices: Normal user, Driver, Shop owner. Normal user opens the email sign-up form; Driver and Shop owner open the invitation-code and phone screen with the role already chosen; Back returns to sign-in</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1895,29 +1921,29 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Emulator, Arabic and English: shop-owner account created; the screen says it is pending and review takes up to 24 hours.</t>
+          <t>Emulator, Arabic and English: Create account asks Normal user / Driver / Shop owner. Normal user opens the email form; Driver and Shop owner open the invitation screen with the role chosen; Back returns to sign-in.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Repeat for the driver (+970590002002)</t>
+          <t>Enter a wrong code</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>The screen says "Application under review" and shows a "Verification documents" card</t>
+          <t>A clear error; you can try again</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1927,29 +1953,29 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Emulator: driver sees 'Application under review' and the Verification documents card.</t>
+          <t>API: a wrong one-time code is refused.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Driver: Add a document → choose licence.jpg (type "Driving licence")</t>
+          <t>Choose Shop owner (invitation code and +970590002003), enter the right code (from otp.txt), then name, a password of at least 15 characters, tick the three consents, Create account</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>It appears in the list as "Driving licence · 1 KB"</t>
+          <t>Account created; the screen says the account is pending and an admin review usually takes up to 24 hours</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -1959,29 +1985,29 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Emulator: licence.jpg uploads through the system file picker and is listed.</t>
+          <t>Emulator, Arabic and English: shop-owner account created; the screen says it is pending and review takes up to 24 hours.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Add vehicle-registration.pdf with type "Vehicle registration"</t>
+          <t>Repeat for the driver (+970590002002)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>It appears in the list</t>
+          <t>The screen says "Application under review" and shows a "Verification documents" card</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -1991,29 +2017,29 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>Emulator: vehicle-registration.pdf uploads and is listed as Vehicle registration.</t>
+          <t>Emulator: driver sees 'Application under review' and the Verification documents card.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Add not-really-an-image.jpg</t>
+          <t>Driver: Add a document → choose licence.jpg (type "Driving licence")</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Refused with "Only JPEG, PNG or PDF files can be uploaded"; nothing added</t>
+          <t>It appears in the list as "Driving licence · 1 KB"</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2023,29 +2049,29 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Emulator: not-really-an-image.jpg is refused with 'Only JPEG, PNG or PDF files can be uploaded'.</t>
+          <t>Emulator: licence.jpg uploads through the system file picker and is listed.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Tap the bin on one document</t>
+          <t>Add vehicle-registration.pdf with type "Vehicle registration"</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>It disappears from the list</t>
+          <t>It appears in the list</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2055,29 +2081,29 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the bin removes a document from the list and from the server.</t>
+          <t>Emulator: vehicle-registration.pdf uploads and is listed as Vehicle registration.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Try to add more than 6 documents</t>
+          <t>Add not-really-an-image.jpg</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>After 6 the Add button is disabled or a limit message shows</t>
+          <t>Refused with "Only JPEG, PNG or PDF files can be uploaded"; nothing added</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2087,29 +2113,29 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>API: the 7th document is refused. The disabled Add button on the phone was not tried.</t>
+          <t>Emulator: not-really-an-image.jpg is refused with 'Only JPEG, PNG or PDF files can be uploaded'.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>In the Admin site, open that driver's review</t>
+          <t>Tap the bin on one document</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>The uploaded documents are listed with a Download button; the downloaded file opens and is the right file</t>
+          <t>It disappears from the list</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2119,29 +2145,29 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>API: the Admin downloads the document, identical bytes, as an attachment. The Download button in the browser was not clicked.</t>
+          <t>Emulator: the bin removes a document from the list and from the server.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Try to sign in on the phone as the new (pending) driver</t>
+          <t>Try to add more than 6 documents</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>You are not let in (account pending), with a clear message</t>
+          <t>After 6 the Add button is disabled or a limit message shows</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2151,29 +2177,29 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>API and emulator: a pending driver cannot sign in (403).</t>
+          <t>API: the 7th document is refused. The disabled Add button on the phone was not tried.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Admin approves that driver (A13), then press Refresh in the app's pending screen</t>
+          <t>In the Admin site, open that driver's review</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>It now says approved and offers sign-in; sign-in works</t>
+          <t>The uploaded documents are listed with a Download button; the downloaded file opens and is the right file</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2183,29 +2209,29 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Emulator: after approval the app says 'Account approved', and the driver signs in by phone and reaches the driver home.</t>
+          <t>API: the Admin downloads the document, identical bytes, as an attachment. The Download button in the browser was not clicked.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Admin approves the shop owner from C03 (A09), then sign in on the phone with their phone number and password</t>
+          <t>Try to sign in on the phone as the new (pending) driver</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Same pending → approved path; the merchant home opens</t>
+          <t>You are not let in (account pending), with a clear message</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2215,29 +2241,29 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Approval and phone sign-in to the merchant home were checked on the 28 Oct run (and the API suite repeats them); the sign-up entry is the new chooser, checked in C03.</t>
+          <t>API and emulator: a pending driver cannot sign in (403).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Use an invitation code twice, or a code with the wrong phone</t>
+          <t>Admin approves that driver (A13), then press Refresh in the app's pending screen</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Refused without revealing why</t>
+          <t>It now says approved and offers sign-in; sign-in works</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2247,29 +2273,29 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>API: a used code and a wrong phone are refused.</t>
+          <t>Emulator: after approval the app says 'Account approved', and the driver signs in by phone and reaches the driver home.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Sign-in screen → "Check an existing application" with a pending applicant's phone and password</t>
+          <t>Admin approves the shop owner from C03 (A09), then sign in on the phone with their phone number and password</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Shows the application status</t>
+          <t>Same pending → approved path; the merchant home opens</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2279,29 +2305,29 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>API: the application-status endpoint answers 'pending review'. The phone's 'Check an existing application' screen was not tried.</t>
+          <t>Approval and phone sign-in to the merchant home were checked on the 28 Oct run (and the API suite repeats them); the sign-up entry is the new chooser, checked in C03.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Shop owner (pending, from C03): Add a document → choose licence.jpg (type "Commercial register")</t>
+          <t>Use an invitation code twice, or a code with the wrong phone</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>The pending screen shows "Verification documents" asking for the commercial register, national ID and shop photo; the file appears in the list as "Commercial register · 1 KB"</t>
+          <t>Refused without revealing why</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2311,29 +2337,29 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>Emulator, Arabic and English: the shop owner sees the shop-papers card, uploads licence.jpg as Commercial register, and it is listed (1 KB). API: wrong kinds and fake files are refused, limit of six.</t>
+          <t>API: a used code and a wrong phone are refused.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>In the Admin site, Users → the pending shop owner → Approve (or Reject)</t>
+          <t>Sign-in screen → "Check an existing application" with a pending applicant's phone and password</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>The shop owner's documents are listed with a Download button before you decide; the downloaded file opens and is the right file</t>
+          <t>Shows the application status</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2343,29 +2369,29 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>API: the Admin lists and downloads the shop owner's document as an attachment with identical bytes. The Approve card in the browser was not clicked.</t>
+          <t>API: the application-status endpoint answers 'pending review'. The phone's 'Check an existing application' screen was not tried.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>Phone: sign-up with invitation</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Create account → Normal user → name, an email ending in @example.com, a password of at least 12 characters → Sign up; type the six-digit code from email-codes.txt, tick the three documents, Continue; then enter a phone such as +970590003020, Send code, type the code from otp.txt, Continue</t>
+          <t>Shop owner (pending, from C03): Add a document → choose licence.jpg (type "Commercial register")</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>The passenger home opens; no invitation code and no admin approval were needed</t>
+          <t>The pending screen shows "Verification documents" asking for the commercial register, national ID and shop photo; the file appears in the list as "Commercial register · 1 KB"</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2375,29 +2401,29 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Emulator, English: Normal user -&gt; email sign-up -&gt; token from email-codes.txt -&gt; three documents -&gt; phone check with the code from otp.txt -&gt; passenger home. Run after making the demo write email and phone codes to files.</t>
+          <t>Emulator, Arabic and English: the shop owner sees the shop-papers card, uploads licence.jpg as Commercial register, and it is listed (1 KB). API: wrong kinds and fake files are refused, limit of six.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Passenger: open the seeded request and its match</t>
+          <t>In the Admin site, Users → the pending shop owner → Approve (or Reject)</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>The request and a match result are shown</t>
+          <t>The shop owner's documents are listed with a Download button before you decide; the downloaded file opens and is the right file</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2407,29 +2433,29 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
+          <t>API: the Admin lists and downloads the shop owner's document as an attachment with identical bytes. The Approve card in the browser was not clicked.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Merchant: open the seeded order</t>
+          <t>Create account → Normal user → name, an email ending in @example.com, a password of at least 12 characters → Sign up; type the six-digit code from email-codes.txt, tick the three documents, Continue; then enter a phone such as +970590003020, Send code, type the code from otp.txt, Continue</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Five parcels and their batch are shown</t>
+          <t>The passenger home opens; no invitation code and no admin approval were needed</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2439,381 +2465,337 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
+          <t>Emulator, English: Normal user -&gt; email sign-up -&gt; token from email-codes.txt -&gt; three documents -&gt; phone check with the code from otp.txt -&gt; passenger home. Run after making the demo write email and phone codes to files.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
+          <t>Open registration (the local test environment turns it on). Create account → Driver. Leave the invitation code empty (it says "Invitation code (optional)"), enter a new phone such as +970590004001, Send code, type the code from otp.txt</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>One combined passenger+parcel match exists, with a score breakdown</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The code screen opens without any invitation code</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr"/>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Driver (the selected one): open the inbox</t>
+          <t>Enter a wrong code, then the right one; then name, a password of at least 15 characters, tick the three consents, Create account</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>The match is there; the other driver's inbox is empty</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>Account created; the screen says "Upload your documents" (not "Application under review"); the button "Send for review" is disabled and lists what is still needed</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr"/>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Driver: accept the match</t>
+          <t>Add licence.jpg (Driving licence) and vehicle-registration.pdf (Vehicle registration) only</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Exactly one trip is created</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>"Send for review" stays disabled; "Still needed" names the national ID</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr"/>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Emulator: accepting creates exactly one trip.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
+          <t>In the Admin site, look in Users and the driver approvals queue for that driver</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Only the next valid action is offered each time</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The driver is not in the review queue yet; approving or rejecting is refused (not submitted)</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr"/>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: open their trip</t>
+          <t>Add a National ID document, then press "Send for review"</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Both see the same trip and the same latest location; read-only</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The screen changes to "Application under review" and says review usually takes up to 24 hours</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr"/>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Passenger and merchant: bell and Notifications tab</t>
+          <t>In the Admin site open the driver approvals queue</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The driver is listed; the three documents have Download buttons and open correctly; Approve works; the phone then signs in</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Driver: complete the trip</t>
+          <t>Create account → Shop owner with no invitation code (+970590004002); upload commercial register and national ID only</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Trip shows completed on all three phones and in the Admin</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>"Send for review" stays disabled until the shop photo is added; then it submits and the shop owner appears in Users as a pending merchant that can be approved</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Emulator and API: trip Completed everywhere.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Main story (passenger, merchant, driver)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Tracking wording</t>
+          <t>Open registration, start with a phone number that already has an account, type the code from otp.txt, then fill the form</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The first screens look exactly like a new number; only at Create account does it say the registration could not be completed</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr"/>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Driver: Earnings/performance tab</t>
+          <t>Start sign-up again with the same phone number twice, then use the first code</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The older attempt no longer works; only the newest code and screen continue</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr"/>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Same tab, acceptance rate</t>
+          <t>Request a code for the same phone more than 5 times in a day, or start more than 10 sign-ups from the one phone in an hour</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+          <t>The app shows a "too many attempts" message; no further codes are produced in otp.txt</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
+          <t>Sign-in screen → "Check an existing application" for the C20 driver before documents are sent</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>The numbers in E02 move accordingly</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
+          <t>It shows "Upload your documents", not "under review"</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr"/>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Merchant: Reports tab</t>
+          <t>Invitation codes still work: repeat C03 or C04 with a code from invitations.txt</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
+          <t>Created as before; the application is under review at once (no extra "Send for review" step)</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -2823,29 +2805,29 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
+          <t>API: invited driver, passenger and shop owner sign-ups still work and the driver appears in the admin queue with its documents without an extra submit step (run-checks C01-C13).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
+          <t>Create account → Normal user → name, email ending @example.com, password of 12+ characters → Sign up; read the code from the newest line for that email in email-codes.txt and type it</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Confirmation; the sheet says it is not an emergency service</t>
+          <t>The code is six digits (not a long token) and finishes the sign-up; typing the same code again later does not work</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -2855,29 +2837,29 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): register/start emails a six-digit code; it completes the sign-up (201); the same code again is refused; the new account signs in by email. Not typed into the phone screen.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Send 11 reports without any being resolved</t>
+          <t>Start another email sign-up and type a wrong six-digit code five times, then the right code</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>The 11th is refused with a message about too many open reports</t>
+          <t>Each wrong code is refused; after the fifth even the right code is refused and no account exists; start again to get a new code</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -2887,29 +2869,29 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>API: the 11th unresolved report is refused.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): five wrong codes are each refused, then the right code is refused too and no account exists.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Admin: Incidents</t>
+          <t>In the six-digit box try 5 digits, 7 digits, letters, or a space in the middle</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
+          <t>Refused before it is checked (the Continue button stays disabled or the API answers 400)</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -2919,29 +2901,29 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): 5 digits, 7 digits, letters and a space inside are all refused (400).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Smaller features</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Driver: go online/offline</t>
+          <t>Sign-in screen → Forgot password → enter the email; read the code from email-codes.txt; enter email + code + a new password. Also try an email that has no account</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>The state changes once per tap and survives closing the app</t>
+          <t>The screen says the same thing for known and unknown emails and no email is produced for the unknown one; the new password signs in, the old one does not; the same code cannot be used twice</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -2951,29 +2933,29 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): reset start answers {ok:true} for known and unknown emails and writes an email only for the known one; wrong code refused; right code sets the new password (old fails, new works); a used code is refused. The Forgot password screen on the phone was not driven.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>F01</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
+          <t>Forgot password: type a wrong six-digit code five times, then the right one</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>The reset is locked; the right code is refused; ask for a new code</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -2983,29 +2965,29 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): five wrong reset codes lock it; the right code is then refused.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>A pending merchant or driver signs in on the phone</t>
+          <t>Open registration (as C19): Driver, no invitation code, new phone such as +970590005xxx; wrong then right phone code; name, password, consents</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Refused with a clear message</t>
+          <t>Account created with no invitation; the app says "Upload your documents", not "under review" (API: onboarding status documents_required)</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3015,29 +2997,29 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>API and emulator: pending merchant and driver cannot sign in.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): driver registers with no invitation code (wrong phone code refused first); account pending; onboarding status documents_required. Not driven on the phone.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
+          <t>Press "Send for review" (API: POST /onboarding/application/submit) with no documents, then with only the licence and registration</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Refused</t>
+          <t>Refused with 409 documents_required, listing the missing documents (3 first, then 1); nothing is submitted</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3047,29 +3029,29 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>API: rejected driver and disabled merchant cannot sign in.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): submit with no documents: 409 documents_required, 3 missing; with licence and registration: 409, 1 missing.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
+          <t>Admin site: look for that driver in the approvals queue and try to approve or reject by API before it was submitted</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Not reachable</t>
+          <t>Not in the queue; approve and reject answer 409 application_not_submitted; the driver cannot sign in</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3079,29 +3061,29 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the unsubmitted driver is not in the pending queue; approve and reject both answer 409 application_not_submitted; phone sign-in is refused.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Must NOT work (safety)</t>
+          <t>Phone: sign-up (invitation or open)</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+          <t>Add the national ID, press "Send for review" (twice)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>No: uploading is closed once a decision is made</t>
+          <t>Accepted ("Application under review"); a second press does nothing new; the driver is now in the admin queue with three documents</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3111,45 +3093,1973 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>API: once approved or rejected, uploads are refused.</t>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): with the national ID added, submit returns pending_review; a second submit is idempotent; the driver appears in the admin queue with 3 documents.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Passenger: open the seeded request and its match</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>The request and a match result are shown</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: the passenger home shows the seeded request PPU Main Gate -&gt; Bethlehem Center.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Merchant: open the seeded order</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Five parcels and their batch are shown</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: the merchant sees the order with five parcels and the consolidation suggestion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Admin: open the Matching page; if there is no match yet, run matching</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>One combined passenger+parcel match exists, with a score breakdown</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>API: matching creates one combined match, score 93.2%, with the breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Driver (the selected one): open the inbox</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>The match is there; the other driver's inbox is empty</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: the selected driver's inbox shows the match; the demo smoke suite confirms the other driver's inbox is empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Driver: accept the match</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Exactly one trip is created</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: accepting creates exactly one trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Driver: advance pickup → picked up → in transit (and simulate points)</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Only the next valid action is offered each time</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: Pickup started -&gt; Picked up -&gt; In transit -&gt; Delivered -&gt; Completed, one valid action at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Passenger and merchant: open their trip</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Both see the same trip and the same latest location; read-only</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: passenger's My trips shows the completed trip and its map; the merchant's Shipments shows the order completed. Simulated location points were not stepped on the phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Passenger and merchant: bell and Notifications tab</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>A "match accepted" and "trip update" entries; tapping one clears its dot; "Mark all as read" works</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: passenger and merchant each got 6 notifications (match accepted + 5 trip updates); 'Mark all as read' cleared them on the phone and the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Driver: complete the trip</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Trip shows completed on all three phones and in the Admin</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>Emulator and API: trip Completed everywhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Main story (passenger, merchant, driver)</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Tracking wording</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Anywhere location appears it is described as simulated, never as live GPS</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: screens say 'Waiting for location' / 'No location yet'; nothing claims live GPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Driver: Earnings/performance tab</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Completed-trip counts shown; earnings says it is not tracked (no invented amount)</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: Earnings tab shows trust score and completed trips; earnings says it is not tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Same tab, acceptance rate</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Under 5 answered offers it says the rate appears after 5; after accepting/rejecting 5 offers it shows a percentage and "x of y"</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: shows 'Your rate appears after 5 answered offers (0 so far)'. The percentage itself is covered by unit tests, not seen on the phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Driver: reject an offer and accept another (needs fresh offers: reset)</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>The numbers in E02 move accordingly</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Needs five fresh offers answered on the phone; covered by unit tests only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Merchant: Reports tab</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Orders, parcels and deliveries by status; matches the Admin report for that merchant</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: Merchant Reports shows 1 order, 5 parcels, 1 delivery, matching the Admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Passenger on a trip: Report a problem → Delay → write a sentence → Send</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Confirmation; the sheet says it is not an emergency service</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: Report a problem (Delay) sent; it shows in the Admin queue as open. The sheet says it is not an emergency service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Send 11 reports without any being resolved</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>The 11th is refused with a message about too many open reports</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>API: the 11th unresolved report is refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Admin: Incidents</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>The report from E05 is there (see A16); after you resolve it, the passenger gets two new notifications and does not see your internal note</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>API: triage works and the reporter gets notifications. Not clicked through in the Admin browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Driver: go online/offline</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>The state changes once per tap and survives closing the app</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Emulator: the Online/Offline switch changes the state on the server and back, and survives closing the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Passenger (route entry switched on): home → Send a parcel → pick a route and stops, size S or M, receiver name and phone, tick the forbidden-items box → Send parcel</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Submit stays disabled until everything is filled and the box is ticked; the parcel then appears under My parcels as "Finding a driver"; the receiver's phone is shown masked</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Same form: try size L, a phone that is too short, or leave the box unticked</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Large is not offered; the others block Send parcel</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr"/>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Passenger: create parcels until you have 3 in flight, then a 4th</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>The 4th is refused with a message about the maximum number of parcels</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr"/>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Passenger: cancel a parcel that is still "Finding a driver" (confirm the dialog)</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>It becomes Cancelled and the receiver details are shown as erased; once a driver has been offered or assigned the parcel there is no Cancel button</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr"/>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Admin: Deliveries page, "Passenger parcels" section</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>The parcel is listed with its tracking state in English and Arabic; no receiver name, phone or note anywhere</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr"/>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Admin → create three stops and a route, publish it (API: /admin/stops, /admin/service-routes, versions, stops, publish). Needs the route switches (the local test environment turns them on)</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>The route appears in the public route catalogue (GET /routes)</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): stops, route, version, ordered stops and publish through the admin API; the route is in the public catalogue. The route switches (ROUTE_MANAGEMENT_ENABLED, MULTI_ROUTE_ENTRY_ENABLED) are turned on by start.ps1 for the local test environment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Admin → the route's "Estimated fares" tab (API: PUT /admin/service-routes/:id/fares): set seat 15.00, parcel S 7.00, M 9.00 with a reason; then try amount 0, 12.5 agorot, a 2-letter reason, a passenger account, and the same fares again</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Saved with your name in the history; 0, fractions and a too-short reason are refused (400), a passenger is refused (403), saving unchanged fares answers 409 fare_unchanged</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): seat 15.00, parcel S 7.00, M 9.00 saved with the admin in the history; amount 0, a fraction, a 2-letter reason refused (400); passenger 403; unchanged fares 409. The Estimated fares tab was not clicked in the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Passenger requests 2 seats on that route (API: POST /passenger/route-requests); the Admin then raises the seat fare to 20.00; the passenger repeats the same request key, then makes a new one</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>The route list and the request show the fare as an estimate paid directly to the driver (2 x 15.00 = 30.00); after the change the first request still says 15.00 (frozen), a new request says 20.00</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the catalogue shows the fare as an estimate paid directly to the driver; a 2-seat request is 15.00 x 2 = 30.00; after the admin raised the fare to 20.00 the same request key still returns 15.00 / 30.00 (also stored in the database) and a new request gets 20.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Passenger parcel (API: POST /passenger/parcels with an Idempotency-Key): size S, receiver name and phone, forbidden-items box ticked; send the same key again</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Created as "Finding a driver"; the receiver phone is shown masked; the second send returns the same parcel and creates no second one; a different body with the same key is refused (409)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): limits published (3 open, S and M only); a parcel is created with a masked receiver phone; replay returns the same parcel (200, replayed) and the list has one; same key with another body is 409; a short key is 400.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Same call with size L, a 3-digit phone, the box unticked or missing, a drop-off before the pickup, a 1-letter name, or an unknown field</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Each is refused with 400 (or a 4xx for the stops); nothing is created</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): size L, a 3-digit phone, unticked or missing acknowledgement, drop-off before pickup, a 1-letter name and an unknown field are all refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Open that parcel as another passenger, a driver, a shop owner and signed out; then the Admin parcel list (GET /admin/passenger-parcels)</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Others get 404, 403 or 401; the Admin list shows the parcel but no receiver name, phone or note</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): another passenger gets 404 (read and cancel), driver and shop owner 403, anonymous 401; the admin list holds no receiver name, phone or note; a passenger cannot open the admin list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Create parcels until 3 are in flight, then a 4th</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>The 4th is refused with 409 passenger_parcel_limit_reached</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the 4th parcel in flight answers 409 passenger_parcel_limit_reached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Cancel a parcel that is still "Finding a driver"; cancel it again; then create a new one</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Cancelled, receiver name, phone and note erased; a second cancel is refused (409); the freed slot allows a new parcel</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): cancel erases receiver name, phone and note and says so; a second cancel is 409; the freed slot allows a new parcel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>As the sender open the parcel's delivery code (API: GET /parcel-orders/:id/handover, POST .../handover/regenerate)</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>The state never shows the code; "Get a new code" returns a six-digit code once; others get 404; an Admin cannot re-issue it (403)</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): state never contains the code; regenerate returns a six-digit code once and it is not readable afterwards; a stranger gets 404; an admin gets 403 on regenerate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Shop owner → bulk orders (API: POST /merchant/orders/bulk/preview): paste a CSV with 5 rows (one has size Q); also try as a passenger</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>The preview lists the valid orders, the bad row with its row number and an Arabic message, and a batch plan; nothing is created; passengers are refused</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): passenger 403, anonymous 401; preview of 5 rows reports 3 orders and 1 bad row (row 6, row_invalid_size, Arabic message) plus a batch plan, and creates nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Submit the CSV without an Idempotency-Key, then with the bad row and without "skip invalid"</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Both are refused (400) and no order is created</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): no Idempotency-Key is 400; the file with a bad row is 400 bulk_validation_failed and creates nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Submit the valid rows with an Idempotency-Key, then send exactly the same upload again; then submit with "skip invalid"</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>First: 3 orders created; the retry creates nothing (all "replayed", the same order numbers, the order list still has 3); skipping the bad row creates the valid ones and reports 1 failed</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): 3 orders created; the retry returns the same 3 order numbers as replayed (200) and the order list stays at 3; skip_invalid creates the valid ones and reports 1 failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Preview or submit a CSV with 51 rows; then one with exactly 50</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>51 rows: rejected as a whole with csv_too_many_rows and nothing created; 50 rows are accepted by the preview</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): 51 rows: 400 csv_too_many_rows and nothing created; exactly 50 rows are accepted by the preview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>Passenger assistant with no AI key (Assistant on the passenger home): "from Bab Al-Zawiya to Bethlehem Center tomorrow at 8am with 2 seats", and the same in Arabic</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>The rule-based fallback fills pickup, destination, time and 2 seats for review; admins and signed-out users cannot use it; an empty message is refused</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): no AI key is configured on the demo; the rule-based fallback fills pickup, destination, time and 2 seats in English and Arabic; admin and anonymous are refused; an empty message is 400. The assistant screen on the phone was not driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Ask the assistant for a ride to Nablus (English and Arabic)</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>A clear reply that the place is not supported yet, listing the supported places as suggestions</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): a ride to Nablus gets a clarification that the place is not supported, listing Bab Al-Zawiya and the other supported places, in English and Arabic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>E29</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Send the assistant something it cannot read; then Admin → Incidents → uncertain assistant requests (API: GET /admin/ai-uncertain-requests); resolve it with a note</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>A clear request is not queued; the unclear one is queued once with its reason and no passenger identity; resolving needs the current revision, a resolved one cannot be resolved again, and the open count drops</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): a clear request is not queued; unreadable text is queued once with a reason and no passenger identity (open count +1); stale revision 409; resolving works; resolving again 409; passenger 403. The Incidents page list was not opened in the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Passenger with an accepted trip: step the simulated driver (Simulate step) until it is near the pickup, then open Notifications</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Exactly one "your driver is approaching" notification (no coordinates in it), however many steps follow; the shop owner gets none</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): after accepting a trip and stepping the simulated driver three times the passenger has exactly one driver_approaching notification with no coordinates; the shop owner has none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>E31</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>Driver on an in-transit parcel trip: try Delivered with the normal status button, then confirm with no code, and try to confirm as the passenger or shop owner</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>The status route refuses (409 delivery_confirmation_required), no code is 400, other roles 403; the trip stays in transit</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): plain Delivered is refused (409), no code 400, passenger and shop owner 403; the trip stays in transit; the trip view shows no code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>E32</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Shop owner: Get a new code for the order (API: POST /parcel-orders/:id/handover/regenerate); the driver tries to read or re-issue it</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>A six-digit code is returned once, attempts remaining 5; the driver gets 404 for both</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the driver gets 404 on both read and re-issue; the shop owner gets a six-digit code once, attempts remaining 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>E33</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Driver enters a wrong code five times, then the right code; then the shop owner gets a new code</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Wrong codes are refused (422); after five, even the right code is refused (429 handover_locked) and the order shows locked; a new code unlocks it</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): five wrong codes are refused (422); the right code then answers 429 handover_locked and the order shows locked; a new code unlocks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Driver enters the right code; the Admin opens the trip (API: GET /admin/trips/:id)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>The trip becomes delivered; the Admin sees it confirmed by receiver code and not flagged; the code is shown nowhere; confirming again is refused</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the right code delivers the trip; the admin trip detail shows confirmation by receiver_code, not flagged, no code; delivering again is refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>E35</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Passenger rates the finished trip: before completion, 0 and 6 stars, then 5 stars, then again; drivers and shop owners try to rate or read it</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Before completion 409 trip_not_completed; 0, 6 and 4.5 are 400; 5 stars saved (201); a second rating 409 trip_already_rated; the passenger can see only their own rating; drivers get 403/404 and no driver screen or API shows a star rating</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): before completion 409 trip_not_completed; 0, 6 and 4.5 stars 400; driver and shop owner cannot rate or read; 5 stars saved (201); second rating 409 trip_already_rated; the passenger reads only their own; no driver endpoint shows a star rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>After the trip: driver trust score (Admin → user detail) and npm run trust:recompute -w @masari/api against the demo database</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>A whole number from 0 to 100 with its breakdown and calculation time; the Admin sees the same number; the job reports 0 failed and gives the same score when run again</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): after the trip the driver has a whole score 0-100 with a calculation time and a breakdown; the admin user detail shows the same score; npm run trust:recompute -w @masari/api against masari_demo reports 0 failed and leaves the score unchanged; run twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>Second trip: the driver chooses "Receiver unavailable" with no reason, a 9-character reason, a 301-character reason, then a proper reason</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>The first three are refused (400); the proper one delivers the trip, the Admin trip list and detail show it flagged with the reason, and the sender sees how it was confirmed</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): no reason, a 9-character and a 301-character reason are 400; a proper reason delivers the trip; the admin list and detail show it flagged with the reason; the sender sees receiver_unavailable and the reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>Admin approves a new driver with document dates (API: expiry on approve): try a licence date in the past, then valid dates</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>A past date is refused (400 expiry_date_in_past); valid dates are saved and the driver appears under "Expiring soon" (within 30 days); a driver cannot read that list</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): a past date is 400 expiry_date_in_past; valid dates are stored and the driver is in the expiring-soon list; a driver cannot read it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>E39</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>Run the expiry job (npm run documents:expiry -w @masari/api) with the licence ending in 5 days, twice</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>The driver gets one "document expires soon" reminder; the second run adds none; the driver is still approved</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): the expiry job (npm run documents:expiry) sent exactly one reminder for a licence ending in 5 days and none on the second run; the driver stayed approved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>Set the licence date to yesterday (database edit on masari_demo) and run the job again; then try to go online</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>The driver becomes "documents expired", is unverified, gets a notification, and going online is refused with 403 driver_documents_expired; a second run restricts nobody twice; the driver still signs in; the Admin sees the driver under "Awaiting driver"</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): with the licence date set to yesterday in masari_demo the job restricts the driver (documents_expired, unverified, notification); going online is 403 driver_documents_expired; a second run restricts nobody twice; the driver keeps a session; the re-review queue lists them as awaiting the driver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Driver renewal (API: /driver/document-renewal): submit with no file, upload a text file, upload a photo, submit</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>No file: 409; text file: 415; with a photo the application goes to the Admin re-review queue; going online is still refused; passengers cannot use the renewal area</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): submit with no file 409; a text file 415; with a photo it reaches the admin re-review queue; going online is still refused; a passenger cannot use the renewal area. The in-app renewal screen is not built yet (API only, as documented).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>Smaller features</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>Admin approves the renewal: first without new dates, then with a new licence date</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>Without new dates it is refused (400); with a new date the driver is approved and verified again at once, the history shows expired and renewal submitted, going online is no longer refused for documents, and the job does not restrict them again</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): approval without new dates is refused (400); with a new licence date the driver is approved and verified at once, the history shows expired and renewal submitted, going online is no longer refused for documents, and the job does not restrict them again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Admin site: sign in as a passenger (using a passenger's email and password)</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>Refused</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>API: a passenger cannot use the Admin sign-in; an Admin cannot sign in by phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>A pending merchant or driver signs in on the phone</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>Refused with a clear message</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>API and emulator: pending merchant and driver cannot sign in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>After the Admin rejects a driver with a reason, sign in as that driver</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Refused</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>API: rejected driver and disabled merchant cannot sign in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>As a passenger, try to open driver or merchant screens (via the menu only; no URL tricks)</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>Not reachable</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>API: other roles' endpoints return 403; the app shows each role only its own menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Admin downloads a driver document, then the applicant is approved: can the applicant still upload?</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>No: uploading is closed once a decision is made</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>API: once approved or rejected, uploads are refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
           <t>F06</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>Must NOT work (safety)</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>Look through every screen for the words "push notification", "emergency", "live GPS", "payment", "earnings" used as if they work</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>None claim a feature that is not built</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>Spot check of the screens: no claim of push, live GPS, payments or emergency response; earnings say not tracked.</t>
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>F07</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>With the open-registration switch off (OPEN_DRIVER_MERCHANT_SIGNUP_ENABLED=false, the default everywhere except the local test environment), choose Driver and leave the invitation code empty</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>The code field is required; sending without one is refused and no code is produced</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr"/>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Not run in this pass: needs the emulator or a manual check (see the Summary sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>Call POST /api/v1/onboarding/application/submit with a pending driver or shop owner session that is missing a required document (any HTTP client)</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>409 documents_required, listing what is missing; the application is not submitted</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): submit with missing required documents answers 409 documents_required with the missing list, and nothing is submitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Passenger role without an invitation code, even with the switch on</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Refused; passengers always register by email or Google</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>API check (scripts/test-env/new-feature-checks.mjs, run by run-checks.mjs on the live demo API): a passenger sign-up attempt without an invitation code is refused (4xx) even though open registration is on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>Must NOT work (safety)</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>A submitted driver deletes the only file of a required kind</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>Refused (documents_required); replacing it by adding a second file first works</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>API (run-checks C04): deleting the only file of a required kind from a submitted application is refused (409).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
-  <conditionalFormatting sqref="E2:E69">
+  <autoFilter ref="A1:F130"/>
+  <conditionalFormatting sqref="E2:E130">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
